--- a/safety_inspection_forms/013_glock_inspection_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/013_glock_inspection_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'trigger_is_safe_to_use'}</t>
+          <t>trigger_is_safe_to_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Trigger is safe to use'}</t>
+          <t>Trigger is safe to use</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'safety_is_engaged_properly'}</t>
+          <t>safety_is_engaged_properly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Safety is engaged properly'}</t>
+          <t>Safety is engaged properly</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'trigger_is_locked_and_safe'}</t>
+          <t>trigger_is_locked_and_safe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Trigger is locked and safe'}</t>
+          <t>Trigger is locked and safe</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'trigger_is_not_locked_and_safe'}</t>
+          <t>trigger_is_not_locked_and_safe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Trigger is not locked and safe'}</t>
+          <t>Trigger is not locked and safe</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'magazine_release_is_functional'}</t>
+          <t>magazine_release_is_functional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Magazine release is functional'}</t>
+          <t>Magazine release is functional</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'ejector_is_functional'}</t>
+          <t>ejector_is_functional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Ejector is functional'}</t>
+          <t>Ejector is functional</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'magazine_is_properly_seated'}</t>
+          <t>magazine_is_properly_seated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Magazine is properly seated'}</t>
+          <t>Magazine is properly seated</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'chamber_is_clear'}</t>
+          <t>chamber_is_clear</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Chamber is clear'}</t>
+          <t>Chamber is clear</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'barrel_is_free_from_obstructions'}</t>
+          <t>barrel_is_free_from_obstructions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Barrel is free from obstructions'}</t>
+          <t>Barrel is free from obstructions</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'glock_19'}</t>
+          <t>glock_19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 19'}</t>
+          <t>Glock 19</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'glock_20'}</t>
+          <t>glock_20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 20'}</t>
+          <t>Glock 20</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'glock_21'}</t>
+          <t>glock_21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 21'}</t>
+          <t>Glock 21</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'glock_23'}</t>
+          <t>glock_23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 23'}</t>
+          <t>Glock 23</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'glock_24'}</t>
+          <t>glock_24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 24'}</t>
+          <t>Glock 24</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'glock_25'}</t>
+          <t>glock_25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 25'}</t>
+          <t>Glock 25</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'glock_26'}</t>
+          <t>glock_26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 26'}</t>
+          <t>Glock 26</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'glock_27'}</t>
+          <t>glock_27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 27'}</t>
+          <t>Glock 27</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'glock_28'}</t>
+          <t>glock_28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 28'}</t>
+          <t>Glock 28</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'glock_29'}</t>
+          <t>glock_29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 29'}</t>
+          <t>Glock 29</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'glock_30'}</t>
+          <t>glock_30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 30'}</t>
+          <t>Glock 30</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'glock_31'}</t>
+          <t>glock_31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Glock 31'}</t>
+          <t>Glock 31</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Operational'}</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'damaged'}</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Damaged'}</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'functional'}</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Functional'}</t>
+          <t>Functional</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'non-operational'}</t>
+          <t>non-operational</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Operational'}</t>
+          <t>Non-Operational</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'requires_maintenance'}</t>
+          <t>requires_maintenance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Requires Maintenance'}</t>
+          <t>Requires Maintenance</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'incomplete'}</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Incomplete'}</t>
+          <t>Incomplete</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'not_inspected'}</t>
+          <t>not_inspected</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Not Inspected'}</t>
+          <t>Not Inspected</t>
         </is>
       </c>
     </row>
